--- a/data/trans_dic/P62A$jubilacion-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,85; 93,82</t>
+          <t>78,33; 94,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,96; 92,5</t>
+          <t>73,41; 91,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,72; 94,74</t>
+          <t>81,82; 94,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,63; 67,69</t>
+          <t>52,06; 68,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,27; 89,89</t>
+          <t>64,88; 91,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,85; 86,56</t>
+          <t>58,35; 86,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,62; 95,94</t>
+          <t>76,81; 96,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>56,05; 74,56</t>
+          <t>55,24; 74,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,52; 90,49</t>
+          <t>77,78; 91,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70,81; 87,73</t>
+          <t>71,37; 87,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83,48; 93,99</t>
+          <t>82,88; 93,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,58; 68,47</t>
+          <t>56,13; 68,36</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,42; 98,87</t>
+          <t>89,43; 98,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,99; 92,33</t>
+          <t>74,04; 92,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,44; 93,3</t>
+          <t>77,62; 93,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,81; 61,11</t>
+          <t>44,26; 60,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,7; 83,99</t>
+          <t>41,8; 82,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 65,42</t>
+          <t>24,81; 61,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,28; 78,12</t>
+          <t>44,92; 78,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,9; 59,51</t>
+          <t>39,43; 58,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,36; 93,68</t>
+          <t>80,02; 93,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64,56; 81,93</t>
+          <t>63,94; 81,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70,3; 86,77</t>
+          <t>71,44; 86,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,2; 58,06</t>
+          <t>45,6; 58,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,85; 90,99</t>
+          <t>78,98; 91,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,24; 83,4</t>
+          <t>69,74; 83,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,88; 91,43</t>
+          <t>80,63; 91,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,4; 53,75</t>
+          <t>38,58; 53,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,21; 87,76</t>
+          <t>49,54; 88,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,48; 79,01</t>
+          <t>53,43; 78,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,62; 86,66</t>
+          <t>58,1; 85,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,61; 53,73</t>
+          <t>34,34; 53,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76,91; 89,53</t>
+          <t>77,33; 89,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,49; 80,27</t>
+          <t>68,53; 80,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,91; 88,47</t>
+          <t>78,13; 88,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,21; 51,03</t>
+          <t>39,14; 51,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,67; 94,5</t>
+          <t>88,88; 94,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,46; 79,2</t>
+          <t>69,92; 79,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,81; 84,18</t>
+          <t>75,63; 84,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,82; 59,34</t>
+          <t>49,89; 59,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,06; 77,59</t>
+          <t>60,34; 77,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,85; 53,24</t>
+          <t>32,75; 52,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,67; 65,98</t>
+          <t>48,41; 65,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,24; 93,91</t>
+          <t>40,95; 93,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,66; 89,42</t>
+          <t>83,08; 89,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61,69; 71,29</t>
+          <t>62,0; 71,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,82; 77,01</t>
+          <t>68,59; 77,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,12; 87,7</t>
+          <t>49,85; 87,47</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,56; 91,32</t>
+          <t>74,86; 91,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,6; 84,71</t>
+          <t>71,78; 84,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,92; 90,63</t>
+          <t>80,47; 90,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,85; 55,61</t>
+          <t>40,16; 55,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,24; 63,95</t>
+          <t>44,29; 64,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,75; 60,79</t>
+          <t>48,02; 61,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,18; 67,55</t>
+          <t>53,82; 68,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,23; 33,46</t>
+          <t>25,23; 33,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,56; 74,62</t>
+          <t>60,18; 73,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,59; 68,92</t>
+          <t>59,21; 68,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68,86; 77,8</t>
+          <t>68,01; 77,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,0; 40,7</t>
+          <t>32,58; 40,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,95</t>
+          <t>0,0; 47,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,62</t>
+          <t>0,0; 39,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,88</t>
+          <t>0,0; 24,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 14,5</t>
+          <t>7,11; 14,44</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,37</t>
+          <t>1,2; 6,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,23</t>
+          <t>1,05; 5,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,34</t>
+          <t>3,09; 8,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 14,58</t>
+          <t>7,17; 14,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,57</t>
+          <t>1,59; 6,49</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,36</t>
+          <t>0,99; 5,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 7,95</t>
+          <t>3,02; 7,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,61; 91,27</t>
+          <t>86,66; 91,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,12; 79,41</t>
+          <t>73,28; 79,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,9; 86,05</t>
+          <t>80,72; 85,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,75; 54,84</t>
+          <t>48,59; 54,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,09; 43,06</t>
+          <t>34,92; 42,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,35; 39,29</t>
+          <t>31,92; 39,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,68; 47,24</t>
+          <t>39,2; 47,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,28; 71,53</t>
+          <t>30,15; 72,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64,25; 69,5</t>
+          <t>64,61; 69,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55,16; 60,18</t>
+          <t>54,84; 60,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63,05; 68,08</t>
+          <t>62,92; 67,96</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,29; 66,02</t>
+          <t>41,29; 68,37</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68651; 81683</t>
+          <t>68194; 81904</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51102; 64793</t>
+          <t>51422; 64108</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80235; 93015</t>
+          <t>80328; 93195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54527; 70127</t>
+          <t>53933; 71381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27213; 37478</t>
+          <t>27052; 38073</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21913; 32233</t>
+          <t>21728; 32154</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38525; 47618</t>
+          <t>38122; 47708</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35985; 47867</t>
+          <t>35465; 47976</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99814; 116504</t>
+          <t>100151; 117585</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75966; 94113</t>
+          <t>76567; 94006</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123394; 138924</t>
+          <t>122509; 138517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94944; 114888</t>
+          <t>94181; 114714</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67974; 75160</t>
+          <t>67988; 75161</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71539; 88077</t>
+          <t>70628; 88076</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61310; 73873</t>
+          <t>61459; 73799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47215; 65856</t>
+          <t>47702; 64951</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11559; 21720</t>
+          <t>10810; 21447</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9979; 24421</t>
+          <t>9262; 22948</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16476; 28423</t>
+          <t>16344; 28465</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24688; 35919</t>
+          <t>23801; 35559</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81867; 95439</t>
+          <t>81529; 95097</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85680; 108733</t>
+          <t>84865; 108182</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81240; 100271</t>
+          <t>82558; 100435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75989; 97623</t>
+          <t>76673; 97841</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>93333; 107701</t>
+          <t>93484; 108349</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>130004; 154355</t>
+          <t>129076; 154847</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140554; 158898</t>
+          <t>140115; 158955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50354; 70486</t>
+          <t>50583; 70093</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10234; 18629</t>
+          <t>10516; 18827</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31515; 46559</t>
+          <t>31485; 46312</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28771; 42532</t>
+          <t>28515; 41930</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17353; 27742</t>
+          <t>17730; 27561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>107363; 124972</t>
+          <t>107949; 124896</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167136; 195870</t>
+          <t>167217; 195718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>173624; 197156</t>
+          <t>174124; 196795</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71657; 93268</t>
+          <t>71526; 93827</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>320642; 341723</t>
+          <t>321427; 341161</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>242982; 277053</t>
+          <t>244561; 278372</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>258634; 291039</t>
+          <t>261484; 292130</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>147034; 175126</t>
+          <t>147247; 175749</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67879; 87684</t>
+          <t>68191; 87359</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38054; 61675</t>
+          <t>37933; 60260</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68919; 95384</t>
+          <t>69983; 94851</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>136687; 311237</t>
+          <t>135734; 310270</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>397089; 424444</t>
+          <t>394307; 424261</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>287261; 331928</t>
+          <t>288686; 330719</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>337404; 377591</t>
+          <t>336267; 379476</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>314009; 549481</t>
+          <t>312344; 548082</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>62491; 75519</t>
+          <t>61913; 75823</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>109332; 129347</t>
+          <t>109596; 129163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>156728; 175530</t>
+          <t>155841; 175639</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57632; 78455</t>
+          <t>56654; 78500</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44750; 64686</t>
+          <t>44797; 64912</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108178; 137729</t>
+          <t>108802; 138760</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>109654; 139290</t>
+          <t>110977; 140277</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55876; 74105</t>
+          <t>55871; 73973</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111348; 137186</t>
+          <t>110652; 135899</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>222210; 261390</t>
+          <t>224571; 261531</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>275361; 311093</t>
+          <t>271969; 308691</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>119647; 147543</t>
+          <t>118123; 146731</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5554</t>
+          <t>0; 4877</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6217</t>
+          <t>0; 6374</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1752</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2699</t>
+          <t>0; 2655</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19125; 39609</t>
+          <t>19424; 39428</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3343; 17140</t>
+          <t>3233; 16971</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2346; 12999</t>
+          <t>2604; 13573</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5807; 16354</t>
+          <t>6068; 16008</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20785; 41323</t>
+          <t>20319; 41296</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5073; 18746</t>
+          <t>4526; 18515</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3062; 13771</t>
+          <t>2549; 13802</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6497; 16455</t>
+          <t>6243; 16432</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>637471; 671802</t>
+          <t>637882; 672228</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>635496; 690127</t>
+          <t>636914; 691230</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>727248; 773576</t>
+          <t>725623; 772081</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>384935; 432983</t>
+          <t>383638; 432540</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>202158; 248046</t>
+          <t>201156; 247086</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>241008; 292758</t>
+          <t>237849; 294880</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>291483; 347033</t>
+          <t>287914; 346245</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>280137; 661775</t>
+          <t>278969; 667243</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>843049; 911975</t>
+          <t>847715; 916296</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>890366; 971383</t>
+          <t>885287; 970631</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1030013; 1112073</t>
+          <t>1027894; 1110148</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>708049; 1132076</t>
+          <t>708012; 1172297</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$jubilacion-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,33; 94,08</t>
+          <t>79,67; 93,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,41; 91,53</t>
+          <t>72,79; 91,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,82; 94,92</t>
+          <t>81,41; 94,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,06; 68,9</t>
+          <t>52,59; 67,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,88; 91,32</t>
+          <t>63,85; 90,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,35; 86,35</t>
+          <t>59,44; 86,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,81; 96,12</t>
+          <t>77,67; 95,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55,24; 74,73</t>
+          <t>57,32; 75,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>77,78; 91,32</t>
+          <t>77,79; 90,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71,37; 87,63</t>
+          <t>71,55; 87,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82,88; 93,71</t>
+          <t>83,96; 93,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,13; 68,36</t>
+          <t>56,57; 68,6</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,43; 98,87</t>
+          <t>89,46; 98,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,04; 92,33</t>
+          <t>74,57; 92,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,62; 93,21</t>
+          <t>77,82; 93,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,26; 60,27</t>
+          <t>44,94; 61,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,8; 82,94</t>
+          <t>40,45; 82,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,81; 61,47</t>
+          <t>26,97; 64,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,92; 78,24</t>
+          <t>45,39; 78,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,43; 58,91</t>
+          <t>41,17; 59,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,02; 93,34</t>
+          <t>79,49; 93,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63,94; 81,51</t>
+          <t>64,95; 82,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,44; 86,91</t>
+          <t>70,79; 86,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,6; 58,19</t>
+          <t>46,34; 59,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,98; 91,54</t>
+          <t>78,47; 91,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,74; 83,66</t>
+          <t>70,33; 83,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,63; 91,47</t>
+          <t>80,92; 91,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,58; 53,45</t>
+          <t>37,86; 52,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,54; 88,69</t>
+          <t>48,69; 89,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,43; 78,59</t>
+          <t>53,51; 77,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,1; 85,44</t>
+          <t>58,2; 86,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,34; 53,38</t>
+          <t>33,73; 53,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,33; 89,48</t>
+          <t>77,36; 89,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,53; 80,21</t>
+          <t>68,36; 80,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78,13; 88,3</t>
+          <t>77,84; 89,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,14; 51,34</t>
+          <t>38,81; 51,06</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,88; 94,34</t>
+          <t>88,8; 94,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,92; 79,58</t>
+          <t>69,09; 79,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,63; 84,5</t>
+          <t>74,66; 83,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49,89; 59,55</t>
+          <t>50,0; 59,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,34; 77,3</t>
+          <t>59,77; 76,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,75; 52,02</t>
+          <t>33,96; 53,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,41; 65,61</t>
+          <t>48,31; 65,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,95; 93,62</t>
+          <t>36,95; 49,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>83,08; 89,39</t>
+          <t>83,15; 89,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62,0; 71,03</t>
+          <t>62,05; 71,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,59; 77,4</t>
+          <t>68,69; 77,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,85; 87,47</t>
+          <t>47,49; 55,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,86; 91,68</t>
+          <t>74,34; 91,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,78; 84,59</t>
+          <t>71,26; 84,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,47; 90,69</t>
+          <t>81,09; 90,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,16; 55,64</t>
+          <t>40,14; 54,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,29; 64,17</t>
+          <t>44,52; 65,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,02; 61,25</t>
+          <t>47,9; 61,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,82; 68,03</t>
+          <t>53,26; 67,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>25,23; 33,4</t>
+          <t>25,26; 33,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>60,18; 73,92</t>
+          <t>60,14; 73,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,21; 68,96</t>
+          <t>58,32; 68,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68,01; 77,2</t>
+          <t>68,15; 77,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,58; 40,47</t>
+          <t>32,68; 39,88</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,38</t>
+          <t>0,0; 47,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,6</t>
+          <t>0,0; 39,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,47</t>
+          <t>0,0; 26,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,11; 14,44</t>
+          <t>6,69; 14,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,3</t>
+          <t>1,44; 6,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,46</t>
+          <t>0,98; 5,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,16</t>
+          <t>3,46; 8,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,17; 14,57</t>
+          <t>7,23; 14,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,49</t>
+          <t>1,85; 6,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,37</t>
+          <t>0,94; 5,35</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,94</t>
+          <t>3,58; 9,2</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>86,66; 91,33</t>
+          <t>86,52; 91,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>73,28; 79,53</t>
+          <t>73,4; 79,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>80,72; 85,88</t>
+          <t>80,73; 85,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,59; 54,78</t>
+          <t>48,95; 54,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,92; 42,89</t>
+          <t>35,11; 43,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,92; 39,58</t>
+          <t>32,2; 39,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,2; 47,14</t>
+          <t>39,57; 47,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>30,15; 72,12</t>
+          <t>29,23; 34,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>64,61; 69,83</t>
+          <t>64,5; 69,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54,84; 60,13</t>
+          <t>55,07; 60,19</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62,92; 67,96</t>
+          <t>62,95; 68,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,29; 68,37</t>
+          <t>40,09; 44,31</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63095</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>105140</t>
+          <t>119203</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>68194; 81904</t>
+          <t>69367; 81662</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51422; 64108</t>
+          <t>50982; 63928</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80328; 93195</t>
+          <t>79933; 93024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53933; 71381</t>
+          <t>61501; 79441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27052; 38073</t>
+          <t>26619; 37570</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21728; 32154</t>
+          <t>22135; 32295</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38122; 47708</t>
+          <t>38549; 47531</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35465; 47976</t>
+          <t>41612; 54546</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100151; 117585</t>
+          <t>100152; 117037</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>76567; 94006</t>
+          <t>76760; 94121</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122509; 138517</t>
+          <t>124100; 138258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94181; 114714</t>
+          <t>107219; 130029</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56712</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86569</t>
+          <t>97021</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>67988; 75161</t>
+          <t>68010; 75171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70628; 88076</t>
+          <t>71138; 88480</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61459; 73799</t>
+          <t>61617; 73669</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47702; 64951</t>
+          <t>52461; 71810</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10810; 21447</t>
+          <t>10460; 21451</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9262; 22948</t>
+          <t>10069; 24221</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16344; 28465</t>
+          <t>16513; 28553</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23801; 35559</t>
+          <t>28245; 40681</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81529; 95097</t>
+          <t>80986; 95321</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84865; 108182</t>
+          <t>86206; 109376</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82558; 100435</t>
+          <t>81801; 100052</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76673; 97841</t>
+          <t>85884; 109496</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60236</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82403</t>
+          <t>89614</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>93484; 108349</t>
+          <t>92875; 107855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>129076; 154847</t>
+          <t>130169; 154088</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140115; 158955</t>
+          <t>140625; 158734</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50583; 70093</t>
+          <t>54289; 75210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10516; 18827</t>
+          <t>10335; 19044</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31485; 46312</t>
+          <t>31535; 45920</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28515; 41930</t>
+          <t>28563; 42454</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17730; 27561</t>
+          <t>19127; 30323</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>107949; 124896</t>
+          <t>107990; 124355</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167217; 195718</t>
+          <t>166800; 195743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174124; 196795</t>
+          <t>173483; 198681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71526; 93827</t>
+          <t>77666; 102169</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161317</t>
+          <t>175798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>260024</t>
+          <t>59412</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>421342</t>
+          <t>235211</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>321427; 341161</t>
+          <t>321124; 341543</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>244561; 278372</t>
+          <t>241685; 277493</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>261484; 292130</t>
+          <t>258099; 290371</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>147247; 175749</t>
+          <t>160757; 192455</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68191; 87359</t>
+          <t>67552; 85901</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37933; 60260</t>
+          <t>39333; 61411</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>69983; 94851</t>
+          <t>69839; 94139</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>135734; 310270</t>
+          <t>50873; 68359</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>394307; 424261</t>
+          <t>394685; 423222</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>288686; 330719</t>
+          <t>288938; 330840</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>336267; 379476</t>
+          <t>336781; 378510</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>312344; 548082</t>
+          <t>218088; 255548</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67774</t>
+          <t>72249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65012</t>
+          <t>70784</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>132786</t>
+          <t>143033</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>61913; 75823</t>
+          <t>61478; 75652</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>109596; 129163</t>
+          <t>108807; 129257</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>155841; 175639</t>
+          <t>157041; 175938</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56654; 78500</t>
+          <t>60595; 83010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44797; 64912</t>
+          <t>45033; 65892</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108802; 138760</t>
+          <t>108521; 140063</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>110977; 140277</t>
+          <t>109831; 140056</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>55871; 73973</t>
+          <t>61208; 81811</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>110652; 135899</t>
+          <t>110568; 135827</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>224571; 261531</t>
+          <t>221195; 261650</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>271969; 308691</t>
+          <t>272508; 309684</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>118123; 146731</t>
+          <t>128512; 156831</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>12340</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4877</t>
+          <t>0; 4838</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6374</t>
+          <t>0; 6381</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2655</t>
+          <t>0; 2784</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19424; 39428</t>
+          <t>18285; 38878</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3233; 16971</t>
+          <t>3868; 16695</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2604; 13573</t>
+          <t>2436; 13795</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6068; 16008</t>
+          <t>7322; 18925</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20319; 41296</t>
+          <t>20486; 40759</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4526; 18515</t>
+          <t>5289; 19688</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2549; 13802</t>
+          <t>2424; 13767</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6243; 16432</t>
+          <t>7949; 20411</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>409655</t>
+          <t>447057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>429121</t>
+          <t>249365</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>838777</t>
+          <t>696422</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>637882; 672228</t>
+          <t>636822; 671534</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>636914; 691230</t>
+          <t>637961; 690705</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>725623; 772081</t>
+          <t>725719; 772036</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>383638; 432540</t>
+          <t>420963; 472513</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>201156; 247086</t>
+          <t>202254; 249874</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>237849; 294880</t>
+          <t>239898; 292368</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>287914; 346245</t>
+          <t>290663; 346905</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>278969; 667243</t>
+          <t>230685; 270787</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847715; 916296</t>
+          <t>846314; 914237</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>885287; 970631</t>
+          <t>888941; 971648</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1027894; 1110148</t>
+          <t>1028300; 1110779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>708012; 1172297</t>
+          <t>661153; 730775</t>
         </is>
       </c>
     </row>
